--- a/xlsx/換色紀錄表(2405) 26號盤存.xlsx
+++ b/xlsx/換色紀錄表(2405) 26號盤存.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d310cb6cf3413c87/換色紀錄表/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2418" documentId="11_5E6ECF7DCF53E46332B81800EA0B0E848EFA4C99" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FC526353-5C83-EA48-A7D4-EE2246A7461F}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1000001_{DBEBD7AD-3EE7-2247-8F86-BAF394F70D4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="12576" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7500,7 +7500,7 @@
       </c>
       <c r="G2" s="21">
         <f ca="1">TODAY()</f>
-        <v>45755</v>
+        <v>46300</v>
       </c>
       <c r="H2" s="54" t="e">
         <f>TEXT(WEEKDAY(每日用粉紀錄表!#REF!,1),"aaaa")</f>
